--- a/data/trans_orig/IP07A11-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IP07A11-Clase-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de haber podido estar al aire libre en 2007 (tasa de respuesta: 99,6%)</t>
+          <t>Menores según la frecuencia de haber podido estar al aire libre, percibida por el adulto en 2007 (tasa de respuesta: 99,6%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>9311</t>
+          <t>9404</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>19173</t>
+          <t>19471</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>19,57%</t>
+          <t>19,76%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>40,3%</t>
+          <t>40,92%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>15060</t>
+          <t>14712</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>25074</t>
+          <t>24756</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>36,59%</t>
+          <t>35,75%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>60,92%</t>
+          <t>60,15%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>26222</t>
+          <t>26490</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>41417</t>
+          <t>41032</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>29,55%</t>
+          <t>29,85%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>46,67%</t>
+          <t>46,24%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>17433</t>
+          <t>17364</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>28506</t>
+          <t>28309</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>36,64%</t>
+          <t>36,49%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>59,91%</t>
+          <t>59,5%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>12402</t>
+          <t>12318</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>22492</t>
+          <t>22617</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>30,13%</t>
+          <t>29,93%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>54,65%</t>
+          <t>54,95%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>32644</t>
+          <t>32729</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>47601</t>
+          <t>47363</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>36,79%</t>
+          <t>36,88%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>53,64%</t>
+          <t>53,37%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>5749</t>
+          <t>5804</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>14621</t>
+          <t>15406</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>12,08%</t>
+          <t>12,2%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>30,73%</t>
+          <t>32,38%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1941</t>
+          <t>1502</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>8322</t>
+          <t>8400</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>3,65%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>20,22%</t>
+          <t>20,41%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>9261</t>
+          <t>8884</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>21764</t>
+          <t>20404</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>10,44%</t>
+          <t>10,01%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>24,53%</t>
+          <t>22,99%</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3417</t>
+          <t>3687</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,18%</t>
+          <t>7,75%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1146,7 +1146,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>3570</t>
+          <t>3176</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>3,58%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>7654</t>
+          <t>7730</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>15875</t>
+          <t>16722</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>25,54%</t>
+          <t>25,79%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>52,96%</t>
+          <t>55,79%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>5150</t>
+          <t>5644</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>13468</t>
+          <t>13454</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>16,25%</t>
+          <t>17,81%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>42,51%</t>
+          <t>42,46%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>14386</t>
+          <t>15162</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>26762</t>
+          <t>27359</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>23,33%</t>
+          <t>24,59%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>43,41%</t>
+          <t>44,37%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>10044</t>
+          <t>9952</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>18632</t>
+          <t>18861</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>33,51%</t>
+          <t>33,2%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>62,16%</t>
+          <t>62,93%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>12098</t>
+          <t>11992</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>20930</t>
+          <t>21376</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>38,19%</t>
+          <t>37,85%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>66,06%</t>
+          <t>67,47%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>24888</t>
+          <t>24681</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>37694</t>
+          <t>37154</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>40,36%</t>
+          <t>40,03%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>61,13%</t>
+          <t>60,26%</t>
         </is>
       </c>
     </row>
@@ -1640,12 +1640,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1634</t>
+          <t>1384</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>7842</t>
+          <t>7535</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>4,62%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>26,16%</t>
+          <t>25,14%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>2544</t>
+          <t>2635</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>9503</t>
+          <t>9560</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1690,12 +1690,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>8,03%</t>
+          <t>8,32%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>30,0%</t>
+          <t>30,17%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>5268</t>
+          <t>5091</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>14489</t>
+          <t>13761</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>8,54%</t>
+          <t>8,26%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>23,5%</t>
+          <t>22,32%</t>
         </is>
       </c>
     </row>
@@ -1793,7 +1793,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>2528</t>
+          <t>2496</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1808,7 +1808,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>7,98%</t>
+          <t>7,88%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1828,7 +1828,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>2459</t>
+          <t>2192</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>3,56%</t>
         </is>
       </c>
     </row>
@@ -2096,12 +2096,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>6981</t>
+          <t>7295</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>15857</t>
+          <t>16206</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2111,12 +2111,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>21,11%</t>
+          <t>22,05%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>47,94%</t>
+          <t>48,99%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2131,12 +2131,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>15500</t>
+          <t>15516</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>27670</t>
+          <t>26855</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>28,46%</t>
+          <t>28,49%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>50,81%</t>
+          <t>49,31%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>25389</t>
+          <t>25422</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>39785</t>
+          <t>40417</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>29,0%</t>
+          <t>29,04%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>45,45%</t>
+          <t>46,17%</t>
         </is>
       </c>
     </row>
@@ -2209,12 +2209,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>11138</t>
+          <t>11082</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>20735</t>
+          <t>19727</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2224,12 +2224,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>33,67%</t>
+          <t>33,5%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>62,69%</t>
+          <t>59,64%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2244,12 +2244,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>17180</t>
+          <t>17010</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>28945</t>
+          <t>28660</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2259,12 +2259,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>31,55%</t>
+          <t>31,23%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>53,15%</t>
+          <t>52,63%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>31212</t>
+          <t>31260</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>45609</t>
+          <t>45822</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>35,66%</t>
+          <t>35,71%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>52,1%</t>
+          <t>52,35%</t>
         </is>
       </c>
     </row>
@@ -2322,12 +2322,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>2373</t>
+          <t>2576</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>9432</t>
+          <t>9654</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2337,12 +2337,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>7,17%</t>
+          <t>7,79%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>28,51%</t>
+          <t>29,19%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2357,12 +2357,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>6451</t>
+          <t>6110</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>16147</t>
+          <t>15315</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2372,12 +2372,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>11,84%</t>
+          <t>11,22%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>29,65%</t>
+          <t>28,12%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>10633</t>
+          <t>10140</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>22213</t>
+          <t>21772</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2407,12 +2407,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>12,15%</t>
+          <t>11,58%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>25,38%</t>
+          <t>24,87%</t>
         </is>
       </c>
     </row>
@@ -2440,7 +2440,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>3391</t>
+          <t>3608</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2455,7 +2455,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>10,25%</t>
+          <t>10,91%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2510,7 +2510,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>3678</t>
+          <t>3181</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2525,7 +2525,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>3,63%</t>
         </is>
       </c>
     </row>
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>22247</t>
+          <t>22445</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>36792</t>
+          <t>36188</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2793,12 +2793,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>25,13%</t>
+          <t>25,35%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>41,56%</t>
+          <t>40,87%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2813,12 +2813,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>26596</t>
+          <t>26662</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>41549</t>
+          <t>41895</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>28,34%</t>
+          <t>28,41%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>44,27%</t>
+          <t>44,64%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>53533</t>
+          <t>52434</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>73804</t>
+          <t>73558</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>29,35%</t>
+          <t>28,75%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>40,46%</t>
+          <t>40,33%</t>
         </is>
       </c>
     </row>
@@ -2891,12 +2891,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>35266</t>
+          <t>35613</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>49754</t>
+          <t>50414</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2906,12 +2906,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>39,83%</t>
+          <t>40,22%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>56,2%</t>
+          <t>56,94%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2926,12 +2926,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>40002</t>
+          <t>39779</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>55542</t>
+          <t>55912</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2941,12 +2941,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>42,62%</t>
+          <t>42,38%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>59,18%</t>
+          <t>59,57%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>79453</t>
+          <t>78724</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>100529</t>
+          <t>100583</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2976,12 +2976,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>43,56%</t>
+          <t>43,16%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>55,12%</t>
+          <t>55,15%</t>
         </is>
       </c>
     </row>
@@ -3004,12 +3004,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>10627</t>
+          <t>10900</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>22745</t>
+          <t>22756</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3019,12 +3019,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>12,0%</t>
+          <t>12,31%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>25,69%</t>
+          <t>25,7%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3039,12 +3039,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>7007</t>
+          <t>7001</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>17187</t>
+          <t>17451</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3054,12 +3054,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>7,47%</t>
+          <t>7,46%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>18,31%</t>
+          <t>18,59%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3074,12 +3074,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>20439</t>
+          <t>20260</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>36146</t>
+          <t>35801</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3089,12 +3089,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>11,21%</t>
+          <t>11,11%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>19,82%</t>
+          <t>19,63%</t>
         </is>
       </c>
     </row>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>4073</t>
+          <t>4435</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3137,7 +3137,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>5,01%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3157,7 +3157,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>3217</t>
+          <t>3048</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3172,7 +3172,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3192,7 +3192,7 @@
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>5034</t>
+          <t>4558</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3207,7 +3207,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,5%</t>
         </is>
       </c>
     </row>
@@ -3270,7 +3270,7 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>4107</t>
+          <t>3414</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3285,7 +3285,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3305,7 +3305,7 @@
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>4101</t>
+          <t>3442</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3320,7 +3320,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>1,89%</t>
         </is>
       </c>
     </row>
@@ -3460,12 +3460,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>16106</t>
+          <t>15652</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>27923</t>
+          <t>27418</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3475,12 +3475,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>29,56%</t>
+          <t>28,73%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>51,26%</t>
+          <t>50,33%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3495,12 +3495,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>28972</t>
+          <t>27446</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>41343</t>
+          <t>41446</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3510,12 +3510,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>41,31%</t>
+          <t>39,14%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>58,96%</t>
+          <t>59,1%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3530,12 +3530,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>47945</t>
+          <t>48023</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>65639</t>
+          <t>65274</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3545,12 +3545,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>38,48%</t>
+          <t>38,54%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>52,68%</t>
+          <t>52,38%</t>
         </is>
       </c>
     </row>
@@ -3573,12 +3573,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>18507</t>
+          <t>18692</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>29981</t>
+          <t>30501</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3588,12 +3588,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>33,97%</t>
+          <t>34,31%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>55,03%</t>
+          <t>55,99%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>24903</t>
+          <t>23467</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>37050</t>
+          <t>37347</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3623,12 +3623,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>35,51%</t>
+          <t>33,46%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>52,83%</t>
+          <t>53,26%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3643,12 +3643,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>46626</t>
+          <t>45625</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>64060</t>
+          <t>63374</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3658,12 +3658,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>37,42%</t>
+          <t>36,62%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>51,41%</t>
+          <t>50,86%</t>
         </is>
       </c>
     </row>
@@ -3686,12 +3686,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>3056</t>
+          <t>2978</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>10255</t>
+          <t>10427</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3701,12 +3701,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>5,61%</t>
+          <t>5,47%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>18,82%</t>
+          <t>19,14%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3721,12 +3721,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>1855</t>
+          <t>1854</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>8561</t>
+          <t>8705</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3736,12 +3736,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>12,21%</t>
+          <t>12,41%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3756,12 +3756,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>6786</t>
+          <t>6798</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>16309</t>
+          <t>16879</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3771,12 +3771,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>5,46%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>13,09%</t>
+          <t>13,55%</t>
         </is>
       </c>
     </row>
@@ -3799,12 +3799,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>657</t>
+          <t>644</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>5574</t>
+          <t>5627</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3814,12 +3814,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>10,23%</t>
+          <t>10,33%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3869,12 +3869,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>657</t>
+          <t>644</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>5656</t>
+          <t>6194</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3884,12 +3884,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>4,97%</t>
         </is>
       </c>
     </row>
@@ -3917,7 +3917,7 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>2653</t>
+          <t>3042</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3932,7 +3932,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>5,58%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3987,7 +3987,7 @@
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>2095</t>
+          <t>2193</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -4002,7 +4002,7 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,76%</t>
         </is>
       </c>
     </row>
@@ -4142,12 +4142,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>5215</t>
+          <t>5052</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>14237</t>
+          <t>14007</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4157,12 +4157,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>12,48%</t>
+          <t>12,09%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>34,08%</t>
+          <t>33,53%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4177,12 +4177,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>6813</t>
+          <t>6396</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>15773</t>
+          <t>15023</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4192,12 +4192,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>19,0%</t>
+          <t>17,84%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>43,98%</t>
+          <t>41,89%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4212,12 +4212,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>13907</t>
+          <t>14353</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>25868</t>
+          <t>26482</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4227,12 +4227,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>17,91%</t>
+          <t>18,49%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>33,32%</t>
+          <t>34,11%</t>
         </is>
       </c>
     </row>
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>19748</t>
+          <t>20152</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>30615</t>
+          <t>30182</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4270,12 +4270,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>47,27%</t>
+          <t>48,24%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>73,28%</t>
+          <t>72,24%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4290,12 +4290,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>11732</t>
+          <t>11668</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>21188</t>
+          <t>21533</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4305,12 +4305,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>32,71%</t>
+          <t>32,54%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>59,08%</t>
+          <t>60,04%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4325,12 +4325,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>35502</t>
+          <t>34813</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>48782</t>
+          <t>48213</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4340,12 +4340,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>45,73%</t>
+          <t>44,84%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>62,83%</t>
+          <t>62,1%</t>
         </is>
       </c>
     </row>
@@ -4368,12 +4368,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>3900</t>
+          <t>4102</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>12318</t>
+          <t>12345</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4383,12 +4383,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>9,34%</t>
+          <t>9,82%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>29,48%</t>
+          <t>29,55%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4403,12 +4403,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>3848</t>
+          <t>3913</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>11273</t>
+          <t>11278</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4418,12 +4418,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>10,73%</t>
+          <t>10,91%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>31,44%</t>
+          <t>31,45%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4438,12 +4438,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>9329</t>
+          <t>9816</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>20512</t>
+          <t>20769</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4453,12 +4453,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>12,02%</t>
+          <t>12,64%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>26,42%</t>
+          <t>26,75%</t>
         </is>
       </c>
     </row>
@@ -4521,7 +4521,7 @@
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>4291</t>
+          <t>4223</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4536,7 +4536,7 @@
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>11,97%</t>
+          <t>11,78%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4556,7 +4556,7 @@
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>4321</t>
+          <t>4868</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4571,7 +4571,7 @@
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>5,57%</t>
+          <t>6,27%</t>
         </is>
       </c>
     </row>
@@ -4824,12 +4824,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>83912</t>
+          <t>83276</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>110773</t>
+          <t>109617</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -4839,12 +4839,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>28,4%</t>
+          <t>28,19%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>37,5%</t>
+          <t>37,1%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4859,12 +4859,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>115785</t>
+          <t>115409</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>143849</t>
+          <t>143534</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -4874,12 +4874,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>35,39%</t>
+          <t>35,28%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>43,97%</t>
+          <t>43,87%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4894,12 +4894,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>204498</t>
+          <t>205173</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>244210</t>
+          <t>243822</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -4909,12 +4909,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>32,85%</t>
+          <t>32,96%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>39,23%</t>
+          <t>39,16%</t>
         </is>
       </c>
     </row>
@@ -4937,12 +4937,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>130837</t>
+          <t>131196</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>159077</t>
+          <t>159010</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -4952,12 +4952,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>44,29%</t>
+          <t>44,41%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>53,85%</t>
+          <t>53,82%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4972,12 +4972,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>136541</t>
+          <t>138692</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>165422</t>
+          <t>165917</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -4987,12 +4987,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>41,74%</t>
+          <t>42,39%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>50,57%</t>
+          <t>50,72%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5007,12 +5007,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>277923</t>
+          <t>277072</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>316132</t>
+          <t>316396</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -5022,12 +5022,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>44,64%</t>
+          <t>44,5%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>50,78%</t>
+          <t>50,82%</t>
         </is>
       </c>
     </row>
@@ -5050,12 +5050,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>38249</t>
+          <t>39071</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>59717</t>
+          <t>59532</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5065,12 +5065,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>12,95%</t>
+          <t>13,23%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>20,21%</t>
+          <t>20,15%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5085,12 +5085,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>33642</t>
+          <t>33439</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>53422</t>
+          <t>52932</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5100,12 +5100,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>10,28%</t>
+          <t>10,22%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>16,33%</t>
+          <t>16,18%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5120,12 +5120,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>78038</t>
+          <t>80117</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>108255</t>
+          <t>108155</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5135,12 +5135,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>12,53%</t>
+          <t>12,87%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>17,39%</t>
+          <t>17,37%</t>
         </is>
       </c>
     </row>
@@ -5163,12 +5163,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>1559</t>
+          <t>1513</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>9154</t>
+          <t>8837</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5178,82 +5178,82 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
+          <t>0,51%</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>2,99%</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K43" s="2" t="inlineStr">
+        <is>
+          <t>2491</t>
+        </is>
+      </c>
+      <c r="L43" s="2" t="inlineStr">
+        <is>
+          <t>614</t>
+        </is>
+      </c>
+      <c r="M43" s="2" t="inlineStr">
+        <is>
+          <t>6585</t>
+        </is>
+      </c>
+      <c r="N43" s="2" t="inlineStr">
+        <is>
+          <t>0,76%</t>
+        </is>
+      </c>
+      <c r="O43" s="2" t="inlineStr">
+        <is>
+          <t>0,19%</t>
+        </is>
+      </c>
+      <c r="P43" s="2" t="inlineStr">
+        <is>
+          <t>2,01%</t>
+        </is>
+      </c>
+      <c r="Q43" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="R43" s="2" t="inlineStr">
+        <is>
+          <t>6712</t>
+        </is>
+      </c>
+      <c r="S43" s="2" t="inlineStr">
+        <is>
+          <t>3279</t>
+        </is>
+      </c>
+      <c r="T43" s="2" t="inlineStr">
+        <is>
+          <t>11871</t>
+        </is>
+      </c>
+      <c r="U43" s="2" t="inlineStr">
+        <is>
+          <t>1,08%</t>
+        </is>
+      </c>
+      <c r="V43" s="2" t="inlineStr">
+        <is>
           <t>0,53%</t>
         </is>
       </c>
-      <c r="I43" s="2" t="inlineStr">
-        <is>
-          <t>3,1%</t>
-        </is>
-      </c>
-      <c r="J43" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K43" s="2" t="inlineStr">
-        <is>
-          <t>2491</t>
-        </is>
-      </c>
-      <c r="L43" s="2" t="inlineStr">
-        <is>
-          <t>717</t>
-        </is>
-      </c>
-      <c r="M43" s="2" t="inlineStr">
-        <is>
-          <t>5871</t>
-        </is>
-      </c>
-      <c r="N43" s="2" t="inlineStr">
-        <is>
-          <t>0,76%</t>
-        </is>
-      </c>
-      <c r="O43" s="2" t="inlineStr">
-        <is>
-          <t>0,22%</t>
-        </is>
-      </c>
-      <c r="P43" s="2" t="inlineStr">
-        <is>
-          <t>1,79%</t>
-        </is>
-      </c>
-      <c r="Q43" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="R43" s="2" t="inlineStr">
-        <is>
-          <t>6712</t>
-        </is>
-      </c>
-      <c r="S43" s="2" t="inlineStr">
-        <is>
-          <t>3402</t>
-        </is>
-      </c>
-      <c r="T43" s="2" t="inlineStr">
-        <is>
-          <t>11273</t>
-        </is>
-      </c>
-      <c r="U43" s="2" t="inlineStr">
-        <is>
-          <t>1,08%</t>
-        </is>
-      </c>
-      <c r="V43" s="2" t="inlineStr">
-        <is>
-          <t>0,55%</t>
-        </is>
-      </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,91%</t>
         </is>
       </c>
     </row>
@@ -5281,7 +5281,7 @@
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>2327</t>
+          <t>2320</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5316,7 +5316,7 @@
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>3207</t>
+          <t>3814</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -5331,7 +5331,7 @@
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5351,7 +5351,7 @@
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>4106</t>
+          <t>4134</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -5545,7 +5545,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de haber podido estar al aire libre en 2012 (tasa de respuesta: 98,23%)</t>
+          <t>Menores según la frecuencia de haber podido estar al aire libre, percibida por el adulto en 2012 (tasa de respuesta: 98,23%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5740,12 +5740,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>16546</t>
+          <t>16219</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>26987</t>
+          <t>27104</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5755,12 +5755,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>41,84%</t>
+          <t>41,02%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>68,25%</t>
+          <t>68,54%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5775,12 +5775,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>11822</t>
+          <t>11842</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>21186</t>
+          <t>21544</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5790,12 +5790,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>33,92%</t>
+          <t>33,98%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>60,79%</t>
+          <t>61,82%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5810,12 +5810,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>30972</t>
+          <t>30522</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>44986</t>
+          <t>45358</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5825,12 +5825,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>41,63%</t>
+          <t>41,03%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>60,47%</t>
+          <t>60,97%</t>
         </is>
       </c>
     </row>
@@ -5853,12 +5853,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>9502</t>
+          <t>9233</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>19645</t>
+          <t>19181</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5868,12 +5868,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>24,03%</t>
+          <t>23,35%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>49,68%</t>
+          <t>48,51%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5888,12 +5888,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>9733</t>
+          <t>9878</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>19051</t>
+          <t>19300</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5903,12 +5903,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>27,93%</t>
+          <t>28,34%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>54,67%</t>
+          <t>55,38%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5923,12 +5923,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>21800</t>
+          <t>22169</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>35976</t>
+          <t>35835</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5938,12 +5938,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>29,3%</t>
+          <t>29,8%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>48,36%</t>
+          <t>48,17%</t>
         </is>
       </c>
     </row>
@@ -5966,12 +5966,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>626</t>
+          <t>1069</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>7347</t>
+          <t>7126</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5981,12 +5981,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>18,58%</t>
+          <t>18,02%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6006,7 +6006,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>6665</t>
+          <t>6894</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6021,7 +6021,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>19,12%</t>
+          <t>19,78%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6036,12 +6036,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>3106</t>
+          <t>3158</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>11005</t>
+          <t>11909</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6051,12 +6051,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>4,25%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>14,79%</t>
+          <t>16,01%</t>
         </is>
       </c>
     </row>
@@ -6084,7 +6084,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3986</t>
+          <t>4124</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6099,7 +6099,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>10,08%</t>
+          <t>10,43%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6119,7 +6119,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>3658</t>
+          <t>2686</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6134,7 +6134,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>10,5%</t>
+          <t>7,71%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6154,7 +6154,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>5046</t>
+          <t>4866</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6169,7 +6169,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,78%</t>
+          <t>6,54%</t>
         </is>
       </c>
     </row>
@@ -6422,12 +6422,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>13688</t>
+          <t>13449</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>23285</t>
+          <t>23252</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6437,12 +6437,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>39,43%</t>
+          <t>38,74%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>67,08%</t>
+          <t>66,98%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6457,12 +6457,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>18488</t>
+          <t>18219</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>27477</t>
+          <t>27775</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>52,67%</t>
+          <t>51,9%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>78,28%</t>
+          <t>79,12%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6492,12 +6492,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>35392</t>
+          <t>34854</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>48339</t>
+          <t>47885</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>50,69%</t>
+          <t>49,92%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>69,24%</t>
+          <t>68,59%</t>
         </is>
       </c>
     </row>
@@ -6535,12 +6535,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>10195</t>
+          <t>10385</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>19542</t>
+          <t>20155</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6550,12 +6550,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>29,37%</t>
+          <t>29,92%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>56,3%</t>
+          <t>58,06%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6570,12 +6570,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>6577</t>
+          <t>6457</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>15096</t>
+          <t>15631</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6585,12 +6585,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>18,74%</t>
+          <t>18,39%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>43,0%</t>
+          <t>44,53%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6605,12 +6605,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>19329</t>
+          <t>19506</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>31925</t>
+          <t>32531</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6620,12 +6620,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>27,68%</t>
+          <t>27,94%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>45,73%</t>
+          <t>46,6%</t>
         </is>
       </c>
     </row>
@@ -6653,7 +6653,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>4139</t>
+          <t>4620</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6668,7 +6668,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>11,92%</t>
+          <t>13,31%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6688,7 +6688,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>3786</t>
+          <t>3088</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6703,7 +6703,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>10,79%</t>
+          <t>8,8%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6718,12 +6718,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>637</t>
+          <t>636</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>5858</t>
+          <t>5008</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6738,7 +6738,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>8,39%</t>
+          <t>7,17%</t>
         </is>
       </c>
     </row>
@@ -6801,7 +6801,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>3170</t>
+          <t>3251</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6816,7 +6816,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>9,03%</t>
+          <t>9,26%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6836,7 +6836,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>3172</t>
+          <t>3380</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6851,7 +6851,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>4,84%</t>
         </is>
       </c>
     </row>
@@ -7104,12 +7104,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>10568</t>
+          <t>10169</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>21122</t>
+          <t>20616</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7119,12 +7119,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>23,85%</t>
+          <t>22,95%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>47,66%</t>
+          <t>46,52%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7139,12 +7139,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>10261</t>
+          <t>10312</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>19520</t>
+          <t>18962</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7154,12 +7154,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>32,05%</t>
+          <t>32,21%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>60,98%</t>
+          <t>59,23%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7174,12 +7174,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>23160</t>
+          <t>23190</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>37287</t>
+          <t>37350</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7189,12 +7189,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>30,34%</t>
+          <t>30,38%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>48,85%</t>
+          <t>48,93%</t>
         </is>
       </c>
     </row>
@@ -7217,12 +7217,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>16723</t>
+          <t>16886</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>27790</t>
+          <t>27371</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7232,12 +7232,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>37,74%</t>
+          <t>38,1%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>62,71%</t>
+          <t>61,76%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7252,12 +7252,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>9825</t>
+          <t>10354</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>18837</t>
+          <t>18995</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7267,12 +7267,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>30,69%</t>
+          <t>32,34%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>58,84%</t>
+          <t>59,33%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7287,12 +7287,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>29744</t>
+          <t>29442</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>43558</t>
+          <t>44293</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7302,12 +7302,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>38,97%</t>
+          <t>38,57%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>57,07%</t>
+          <t>58,03%</t>
         </is>
       </c>
     </row>
@@ -7330,12 +7330,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>2657</t>
+          <t>2703</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>10301</t>
+          <t>10736</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -7345,12 +7345,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>23,25%</t>
+          <t>24,23%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -7365,12 +7365,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>620</t>
+          <t>613</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>5609</t>
+          <t>5514</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -7380,12 +7380,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>17,52%</t>
+          <t>17,22%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -7400,12 +7400,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>4398</t>
+          <t>4567</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>13580</t>
+          <t>13240</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -7415,12 +7415,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>5,76%</t>
+          <t>5,98%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>17,79%</t>
+          <t>17,35%</t>
         </is>
       </c>
     </row>
@@ -7448,7 +7448,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>3340</t>
+          <t>2733</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7463,7 +7463,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>7,54%</t>
+          <t>6,17%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7483,7 +7483,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>4466</t>
+          <t>3576</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7498,7 +7498,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>13,95%</t>
+          <t>11,17%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7518,7 +7518,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>4723</t>
+          <t>4716</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7533,7 +7533,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>6,19%</t>
+          <t>6,18%</t>
         </is>
       </c>
     </row>
@@ -7786,12 +7786,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>44918</t>
+          <t>44617</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>60178</t>
+          <t>60225</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7801,12 +7801,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>51,71%</t>
+          <t>51,37%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>69,28%</t>
+          <t>69,34%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7821,12 +7821,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>49235</t>
+          <t>49675</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>65611</t>
+          <t>66494</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7836,12 +7836,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>49,17%</t>
+          <t>49,61%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>65,53%</t>
+          <t>66,41%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7856,12 +7856,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>98813</t>
+          <t>99671</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>121449</t>
+          <t>121285</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7871,12 +7871,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>52,84%</t>
+          <t>53,3%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>64,95%</t>
+          <t>64,86%</t>
         </is>
       </c>
     </row>
@@ -7899,12 +7899,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>22233</t>
+          <t>21774</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>37062</t>
+          <t>36770</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -7914,12 +7914,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>25,6%</t>
+          <t>25,07%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>42,67%</t>
+          <t>42,33%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -7934,12 +7934,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>26365</t>
+          <t>25081</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>42289</t>
+          <t>40990</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -7949,12 +7949,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>26,33%</t>
+          <t>25,05%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>42,24%</t>
+          <t>40,94%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -7969,12 +7969,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>52040</t>
+          <t>52749</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>74540</t>
+          <t>74066</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -7984,12 +7984,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>27,83%</t>
+          <t>28,21%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>39,86%</t>
+          <t>39,61%</t>
         </is>
       </c>
     </row>
@@ -8012,12 +8012,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1965</t>
+          <t>2435</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>10206</t>
+          <t>10444</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -8027,12 +8027,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>11,75%</t>
+          <t>12,02%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -8047,12 +8047,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>3165</t>
+          <t>3818</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>12486</t>
+          <t>12864</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -8062,12 +8062,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,81%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>12,47%</t>
+          <t>12,85%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -8082,12 +8082,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>7233</t>
+          <t>7378</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>17857</t>
+          <t>18538</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -8097,12 +8097,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>9,55%</t>
+          <t>9,91%</t>
         </is>
       </c>
     </row>
@@ -8165,7 +8165,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>3811</t>
+          <t>3801</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -8180,7 +8180,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -8200,7 +8200,7 @@
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>3751</t>
+          <t>4089</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -8215,7 +8215,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>2,19%</t>
         </is>
       </c>
     </row>
@@ -8468,12 +8468,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>35505</t>
+          <t>36093</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>49949</t>
+          <t>50155</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -8483,12 +8483,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>46,67%</t>
+          <t>47,44%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>65,65%</t>
+          <t>65,93%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -8503,12 +8503,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>32748</t>
+          <t>32582</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>46510</t>
+          <t>46562</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -8518,12 +8518,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>45,44%</t>
+          <t>45,21%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>64,54%</t>
+          <t>64,61%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -8538,12 +8538,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>72144</t>
+          <t>72490</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>91355</t>
+          <t>92827</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -8553,12 +8553,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>48,7%</t>
+          <t>48,93%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>61,67%</t>
+          <t>62,66%</t>
         </is>
       </c>
     </row>
@@ -8581,12 +8581,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>18489</t>
+          <t>17914</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>31659</t>
+          <t>31208</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -8596,12 +8596,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>24,3%</t>
+          <t>23,55%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>41,61%</t>
+          <t>41,02%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -8616,12 +8616,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>20390</t>
+          <t>21434</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>34493</t>
+          <t>34565</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -8631,12 +8631,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>28,29%</t>
+          <t>29,74%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>47,86%</t>
+          <t>47,96%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -8651,12 +8651,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>43661</t>
+          <t>42145</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>62107</t>
+          <t>61094</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -8666,12 +8666,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>29,47%</t>
+          <t>28,45%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>41,92%</t>
+          <t>41,24%</t>
         </is>
       </c>
     </row>
@@ -8694,12 +8694,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>4018</t>
+          <t>3842</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>13487</t>
+          <t>13091</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -8709,12 +8709,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>5,28%</t>
+          <t>5,05%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>17,73%</t>
+          <t>17,21%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -8729,12 +8729,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>1349</t>
+          <t>1356</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>7709</t>
+          <t>8114</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -8744,12 +8744,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>10,7%</t>
+          <t>11,26%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -8764,12 +8764,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>7033</t>
+          <t>6692</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>18168</t>
+          <t>17796</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -8779,12 +8779,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>4,52%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>12,26%</t>
+          <t>12,01%</t>
         </is>
       </c>
     </row>
@@ -8812,7 +8812,7 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>3572</t>
+          <t>3199</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -8827,7 +8827,7 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -8847,7 +8847,7 @@
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>3497</t>
+          <t>3849</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -8862,7 +8862,7 @@
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>5,34%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -8882,7 +8882,7 @@
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>5402</t>
+          <t>5162</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -8897,7 +8897,7 @@
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,48%</t>
         </is>
       </c>
     </row>
@@ -8960,7 +8960,7 @@
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>3491</t>
+          <t>3629</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -8975,7 +8975,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>5,04%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -8995,7 +8995,7 @@
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>3462</t>
+          <t>4186</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -9010,7 +9010,7 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,83%</t>
         </is>
       </c>
     </row>
@@ -9150,12 +9150,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>7051</t>
+          <t>7177</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>15124</t>
+          <t>14731</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -9165,12 +9165,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>28,34%</t>
+          <t>28,84%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>60,78%</t>
+          <t>59,2%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -9185,12 +9185,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>12266</t>
+          <t>11636</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>22623</t>
+          <t>22182</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -9200,12 +9200,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>32,79%</t>
+          <t>31,1%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>60,47%</t>
+          <t>59,29%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -9220,12 +9220,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>21922</t>
+          <t>21469</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>34823</t>
+          <t>33877</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -9235,12 +9235,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>35,19%</t>
+          <t>34,46%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>55,9%</t>
+          <t>54,38%</t>
         </is>
       </c>
     </row>
@@ -9263,12 +9263,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>8601</t>
+          <t>8884</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>16742</t>
+          <t>16404</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -9278,12 +9278,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>34,57%</t>
+          <t>35,7%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>67,29%</t>
+          <t>65,93%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -9298,12 +9298,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>12754</t>
+          <t>13011</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>23373</t>
+          <t>23345</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -9313,12 +9313,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>34,09%</t>
+          <t>34,78%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>62,48%</t>
+          <t>62,4%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -9333,12 +9333,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>24002</t>
+          <t>24582</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>36780</t>
+          <t>37212</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -9348,12 +9348,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>38,53%</t>
+          <t>39,46%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>59,04%</t>
+          <t>59,74%</t>
         </is>
       </c>
     </row>
@@ -9381,7 +9381,7 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>4467</t>
+          <t>3837</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -9396,7 +9396,7 @@
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>17,95%</t>
+          <t>15,42%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -9411,12 +9411,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>431</t>
+          <t>441</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>4912</t>
+          <t>4696</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -9426,12 +9426,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>13,13%</t>
+          <t>12,55%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -9446,12 +9446,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>1038</t>
+          <t>902</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>6832</t>
+          <t>7014</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -9461,12 +9461,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>10,97%</t>
+          <t>11,26%</t>
         </is>
       </c>
     </row>
@@ -9642,57 +9642,57 @@
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
+          <t>3012</t>
+        </is>
+      </c>
+      <c r="N38" s="2" t="inlineStr">
+        <is>
+          <t>1,62%</t>
+        </is>
+      </c>
+      <c r="O38" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="P38" s="2" t="inlineStr">
+        <is>
+          <t>8,05%</t>
+        </is>
+      </c>
+      <c r="Q38" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R38" s="2" t="inlineStr">
+        <is>
+          <t>607</t>
+        </is>
+      </c>
+      <c r="S38" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T38" s="2" t="inlineStr">
+        <is>
           <t>3092</t>
         </is>
       </c>
-      <c r="N38" s="2" t="inlineStr">
-        <is>
-          <t>1,62%</t>
-        </is>
-      </c>
-      <c r="O38" s="2" t="inlineStr">
+      <c r="U38" s="2" t="inlineStr">
+        <is>
+          <t>0,97%</t>
+        </is>
+      </c>
+      <c r="V38" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P38" s="2" t="inlineStr">
-        <is>
-          <t>8,26%</t>
-        </is>
-      </c>
-      <c r="Q38" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R38" s="2" t="inlineStr">
-        <is>
-          <t>607</t>
-        </is>
-      </c>
-      <c r="S38" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T38" s="2" t="inlineStr">
-        <is>
-          <t>3264</t>
-        </is>
-      </c>
-      <c r="U38" s="2" t="inlineStr">
-        <is>
-          <t>0,97%</t>
-        </is>
-      </c>
-      <c r="V38" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>5,24%</t>
+          <t>4,96%</t>
         </is>
       </c>
     </row>
@@ -9832,12 +9832,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>147292</t>
+          <t>147576</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>175725</t>
+          <t>176685</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -9847,12 +9847,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>48,07%</t>
+          <t>48,17%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>57,35%</t>
+          <t>57,67%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -9867,12 +9867,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>153707</t>
+          <t>156059</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>183595</t>
+          <t>183393</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -9882,12 +9882,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>49,33%</t>
+          <t>50,09%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>58,93%</t>
+          <t>58,86%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -9902,12 +9902,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>313095</t>
+          <t>310651</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>353414</t>
+          <t>350831</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -9917,12 +9917,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>50,67%</t>
+          <t>50,27%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>57,19%</t>
+          <t>56,77%</t>
         </is>
       </c>
     </row>
@@ -9945,12 +9945,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>105184</t>
+          <t>103226</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>132486</t>
+          <t>132708</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -9960,12 +9960,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>34,33%</t>
+          <t>33,69%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>43,24%</t>
+          <t>43,31%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -9980,12 +9980,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>106168</t>
+          <t>105229</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>134825</t>
+          <t>132605</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -9995,12 +9995,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>34,08%</t>
+          <t>33,77%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>43,27%</t>
+          <t>42,56%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -10015,12 +10015,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>216148</t>
+          <t>216596</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>254844</t>
+          <t>255779</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -10030,12 +10030,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>34,98%</t>
+          <t>35,05%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>41,24%</t>
+          <t>41,39%</t>
         </is>
       </c>
     </row>
@@ -10058,12 +10058,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>17644</t>
+          <t>17089</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>33698</t>
+          <t>34587</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -10073,12 +10073,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>5,76%</t>
+          <t>5,58%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>11,0%</t>
+          <t>11,29%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -10093,12 +10093,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>13088</t>
+          <t>12011</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>27088</t>
+          <t>25708</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -10108,12 +10108,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>8,69%</t>
+          <t>8,25%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -10128,12 +10128,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>33492</t>
+          <t>33644</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>54655</t>
+          <t>54144</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -10143,12 +10143,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>5,42%</t>
+          <t>5,44%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>8,84%</t>
+          <t>8,76%</t>
         </is>
       </c>
     </row>
@@ -10171,12 +10171,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>296</t>
+          <t>629</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>5647</t>
+          <t>6288</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -10186,12 +10186,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>0,1%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -10206,12 +10206,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>1412</t>
+          <t>1400</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>8860</t>
+          <t>8592</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -10226,7 +10226,7 @@
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -10241,12 +10241,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>2764</t>
+          <t>2639</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>10646</t>
+          <t>10963</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -10256,12 +10256,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,77%</t>
         </is>
       </c>
     </row>
@@ -10324,7 +10324,7 @@
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>4565</t>
+          <t>3967</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -10339,7 +10339,7 @@
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -10359,7 +10359,7 @@
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>4600</t>
+          <t>4182</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -10374,7 +10374,7 @@
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,68%</t>
         </is>
       </c>
     </row>
@@ -10553,7 +10553,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de haber podido estar al aire libre en 2016 (tasa de respuesta: 98,92%)</t>
+          <t>Menores según la frecuencia de haber podido estar al aire libre, percibida por el adulto en 2016 (tasa de respuesta: 98,92%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -10748,12 +10748,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>16182</t>
+          <t>16027</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>25485</t>
+          <t>25994</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -10763,12 +10763,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>46,75%</t>
+          <t>46,3%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>73,62%</t>
+          <t>75,09%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -10783,12 +10783,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>15676</t>
+          <t>16107</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>25919</t>
+          <t>26381</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -10798,12 +10798,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>40,94%</t>
+          <t>42,07%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>67,69%</t>
+          <t>68,9%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10818,12 +10818,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>35497</t>
+          <t>35228</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>48968</t>
+          <t>49190</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -10833,12 +10833,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>48,69%</t>
+          <t>48,32%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>67,16%</t>
+          <t>67,47%</t>
         </is>
       </c>
     </row>
@@ -10861,12 +10861,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>8077</t>
+          <t>7652</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>17316</t>
+          <t>17247</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -10876,12 +10876,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>23,33%</t>
+          <t>22,1%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>50,02%</t>
+          <t>49,82%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10896,12 +10896,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>9713</t>
+          <t>9327</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>18973</t>
+          <t>19645</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -10911,12 +10911,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>25,37%</t>
+          <t>24,36%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>49,55%</t>
+          <t>51,3%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10931,12 +10931,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>19914</t>
+          <t>18753</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>32945</t>
+          <t>32892</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -10946,12 +10946,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>27,31%</t>
+          <t>25,72%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>45,19%</t>
+          <t>45,11%</t>
         </is>
       </c>
     </row>
@@ -10979,7 +10979,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2533</t>
+          <t>3070</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -10994,7 +10994,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>7,32%</t>
+          <t>8,87%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -11009,12 +11009,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>661</t>
+          <t>656</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>6086</t>
+          <t>6242</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -11024,12 +11024,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>15,89%</t>
+          <t>16,3%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -11044,12 +11044,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1270</t>
+          <t>1228</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>7203</t>
+          <t>7175</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -11059,12 +11059,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>9,88%</t>
+          <t>9,84%</t>
         </is>
       </c>
     </row>
@@ -11092,7 +11092,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4143</t>
+          <t>3869</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -11107,7 +11107,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>11,97%</t>
+          <t>11,18%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -11162,7 +11162,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>4132</t>
+          <t>3888</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -11177,7 +11177,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>5,33%</t>
         </is>
       </c>
     </row>
@@ -11240,7 +11240,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>2798</t>
+          <t>2880</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -11255,7 +11255,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>7,31%</t>
+          <t>7,52%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11275,7 +11275,7 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2485</t>
+          <t>3112</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -11290,7 +11290,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>4,27%</t>
         </is>
       </c>
     </row>
@@ -11430,12 +11430,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>21853</t>
+          <t>21035</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>33809</t>
+          <t>33003</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -11445,12 +11445,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>42,14%</t>
+          <t>40,56%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>65,19%</t>
+          <t>63,64%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11465,12 +11465,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>17119</t>
+          <t>16690</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>28944</t>
+          <t>28779</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -11480,12 +11480,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>35,34%</t>
+          <t>34,45%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>59,75%</t>
+          <t>59,41%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11500,12 +11500,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>42011</t>
+          <t>42518</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>59148</t>
+          <t>59051</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -11515,12 +11515,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>41,88%</t>
+          <t>42,39%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>58,97%</t>
+          <t>58,87%</t>
         </is>
       </c>
     </row>
@@ -11543,12 +11543,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>13389</t>
+          <t>13413</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>24817</t>
+          <t>25142</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -11558,12 +11558,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>25,82%</t>
+          <t>25,86%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>47,86%</t>
+          <t>48,48%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -11578,12 +11578,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>13854</t>
+          <t>13452</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>25921</t>
+          <t>24978</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -11593,12 +11593,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>28,6%</t>
+          <t>27,77%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>53,51%</t>
+          <t>51,56%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -11613,12 +11613,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>29974</t>
+          <t>30419</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>46222</t>
+          <t>46180</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -11628,12 +11628,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>29,88%</t>
+          <t>30,33%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>46,08%</t>
+          <t>46,04%</t>
         </is>
       </c>
     </row>
@@ -11656,12 +11656,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2144</t>
+          <t>2316</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>9795</t>
+          <t>9908</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -11671,12 +11671,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>4,47%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>18,89%</t>
+          <t>19,1%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -11691,12 +11691,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>2659</t>
+          <t>2688</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>10256</t>
+          <t>10202</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -11706,12 +11706,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>5,55%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>21,17%</t>
+          <t>21,06%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -11726,12 +11726,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>6182</t>
+          <t>6589</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>16521</t>
+          <t>17822</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -11741,12 +11741,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>6,16%</t>
+          <t>6,57%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>16,47%</t>
+          <t>17,77%</t>
         </is>
       </c>
     </row>
@@ -11809,7 +11809,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>3937</t>
+          <t>4317</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -11824,7 +11824,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,13%</t>
+          <t>8,91%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -11844,7 +11844,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>3600</t>
+          <t>4333</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -11859,7 +11859,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>4,32%</t>
         </is>
       </c>
     </row>
@@ -12112,12 +12112,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>8804</t>
+          <t>9153</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>18172</t>
+          <t>18198</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -12127,12 +12127,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>31,33%</t>
+          <t>32,57%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>64,66%</t>
+          <t>64,76%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12147,12 +12147,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>15204</t>
+          <t>15906</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>26081</t>
+          <t>26043</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -12162,12 +12162,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>37,08%</t>
+          <t>38,79%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>63,6%</t>
+          <t>63,51%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12182,12 +12182,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>27166</t>
+          <t>27232</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>40888</t>
+          <t>41526</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -12197,12 +12197,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>39,31%</t>
+          <t>39,41%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>59,17%</t>
+          <t>60,09%</t>
         </is>
       </c>
     </row>
@@ -12225,12 +12225,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>4855</t>
+          <t>5075</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>13194</t>
+          <t>13339</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -12240,12 +12240,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>17,28%</t>
+          <t>18,06%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>46,95%</t>
+          <t>47,47%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12260,12 +12260,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>11752</t>
+          <t>11536</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>22120</t>
+          <t>22123</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -12275,12 +12275,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>28,66%</t>
+          <t>28,13%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>53,94%</t>
+          <t>53,95%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12295,12 +12295,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>19814</t>
+          <t>19702</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>33364</t>
+          <t>33027</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -12310,12 +12310,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>28,67%</t>
+          <t>28,51%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>48,28%</t>
+          <t>47,79%</t>
         </is>
       </c>
     </row>
@@ -12338,12 +12338,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1473</t>
+          <t>1422</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>7981</t>
+          <t>8125</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -12353,12 +12353,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>5,24%</t>
+          <t>5,06%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>28,4%</t>
+          <t>28,91%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -12373,12 +12373,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>699</t>
+          <t>710</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>6255</t>
+          <t>6640</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -12388,12 +12388,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>15,26%</t>
+          <t>16,19%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -12408,12 +12408,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>3319</t>
+          <t>3375</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>11454</t>
+          <t>11415</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -12423,12 +12423,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>4,88%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>16,57%</t>
+          <t>16,52%</t>
         </is>
       </c>
     </row>
@@ -12456,7 +12456,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>4796</t>
+          <t>5432</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -12471,7 +12471,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>17,07%</t>
+          <t>19,33%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -12491,7 +12491,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>3598</t>
+          <t>3153</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -12506,7 +12506,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>8,78%</t>
+          <t>7,69%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -12526,7 +12526,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>5863</t>
+          <t>6060</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -12541,7 +12541,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>8,48%</t>
+          <t>8,77%</t>
         </is>
       </c>
     </row>
@@ -12569,7 +12569,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>2681</t>
+          <t>3121</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -12584,7 +12584,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>9,54%</t>
+          <t>11,11%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12639,7 +12639,7 @@
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>3735</t>
+          <t>3305</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -12654,7 +12654,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>4,78%</t>
         </is>
       </c>
     </row>
@@ -12794,12 +12794,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>47198</t>
+          <t>46824</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>64753</t>
+          <t>64209</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -12809,12 +12809,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>41,0%</t>
+          <t>40,67%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>56,25%</t>
+          <t>55,77%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12829,12 +12829,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>43371</t>
+          <t>44434</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>61390</t>
+          <t>61917</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -12844,12 +12844,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>41,89%</t>
+          <t>42,92%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>59,29%</t>
+          <t>59,8%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12864,12 +12864,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>96679</t>
+          <t>96617</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>120758</t>
+          <t>121464</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -12879,12 +12879,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>44,21%</t>
+          <t>44,19%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>55,23%</t>
+          <t>55,55%</t>
         </is>
       </c>
     </row>
@@ -12907,12 +12907,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>31286</t>
+          <t>30723</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>47634</t>
+          <t>47019</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -12922,12 +12922,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>27,18%</t>
+          <t>26,69%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>41,38%</t>
+          <t>40,84%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -12942,12 +12942,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>34745</t>
+          <t>33224</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>52300</t>
+          <t>51141</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -12957,12 +12957,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>33,56%</t>
+          <t>32,09%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>50,51%</t>
+          <t>49,39%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>70737</t>
+          <t>69253</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>93943</t>
+          <t>93365</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -12992,12 +12992,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>32,35%</t>
+          <t>31,67%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>42,96%</t>
+          <t>42,7%</t>
         </is>
       </c>
     </row>
@@ -13020,12 +13020,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>12669</t>
+          <t>12336</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>25345</t>
+          <t>25029</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -13035,12 +13035,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>11,0%</t>
+          <t>10,72%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>22,02%</t>
+          <t>21,74%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -13055,12 +13055,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>3252</t>
+          <t>3302</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>12560</t>
+          <t>12304</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -13070,12 +13070,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>12,13%</t>
+          <t>11,88%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -13090,12 +13090,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>18065</t>
+          <t>17584</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>32916</t>
+          <t>33191</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -13105,12 +13105,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>8,26%</t>
+          <t>8,04%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>15,05%</t>
+          <t>15,18%</t>
         </is>
       </c>
     </row>
@@ -13133,12 +13133,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>718</t>
+          <t>714</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>6605</t>
+          <t>6443</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -13153,7 +13153,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>5,74%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13173,7 +13173,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>4328</t>
+          <t>4210</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -13188,7 +13188,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>4,07%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13203,12 +13203,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1239</t>
+          <t>1337</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>7013</t>
+          <t>8262</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -13218,12 +13218,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,78%</t>
         </is>
       </c>
     </row>
@@ -13286,7 +13286,7 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>4455</t>
+          <t>3768</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -13301,7 +13301,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13321,7 +13321,7 @@
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>3774</t>
+          <t>3786</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -13476,12 +13476,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>29393</t>
+          <t>29018</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>44437</t>
+          <t>43323</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -13491,12 +13491,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>38,65%</t>
+          <t>38,16%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>58,44%</t>
+          <t>56,97%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13511,12 +13511,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>32974</t>
+          <t>32761</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>48211</t>
+          <t>47781</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -13526,12 +13526,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>44,84%</t>
+          <t>44,55%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>65,56%</t>
+          <t>64,97%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13546,12 +13546,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>65744</t>
+          <t>67190</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>86745</t>
+          <t>87745</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -13561,12 +13561,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>43,95%</t>
+          <t>44,92%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>57,99%</t>
+          <t>58,66%</t>
         </is>
       </c>
     </row>
@@ -13589,12 +13589,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>21535</t>
+          <t>22752</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>36437</t>
+          <t>36590</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -13604,12 +13604,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>28,32%</t>
+          <t>29,92%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>47,92%</t>
+          <t>48,12%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13624,12 +13624,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>17548</t>
+          <t>17630</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>30638</t>
+          <t>31127</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -13639,12 +13639,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>23,86%</t>
+          <t>23,97%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>41,66%</t>
+          <t>42,33%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13659,12 +13659,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>43499</t>
+          <t>42839</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>63423</t>
+          <t>62562</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -13674,12 +13674,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>29,08%</t>
+          <t>28,64%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>42,4%</t>
+          <t>41,82%</t>
         </is>
       </c>
     </row>
@@ -13702,12 +13702,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>4125</t>
+          <t>4254</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>13710</t>
+          <t>14075</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -13717,12 +13717,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>5,59%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>18,03%</t>
+          <t>18,51%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -13737,12 +13737,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>4689</t>
+          <t>4756</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>14024</t>
+          <t>14168</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -13752,12 +13752,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>6,38%</t>
+          <t>6,47%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>19,07%</t>
+          <t>19,26%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -13772,12 +13772,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>10548</t>
+          <t>10980</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>24126</t>
+          <t>23629</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -13787,12 +13787,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>7,05%</t>
+          <t>7,34%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>16,13%</t>
+          <t>15,8%</t>
         </is>
       </c>
     </row>
@@ -13820,7 +13820,7 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>3972</t>
+          <t>3914</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -13835,7 +13835,7 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>5,22%</t>
+          <t>5,15%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -13890,7 +13890,7 @@
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>4144</t>
+          <t>3874</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -13905,7 +13905,7 @@
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,59%</t>
         </is>
       </c>
     </row>
@@ -13933,7 +13933,7 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>4931</t>
+          <t>4661</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -13948,7 +13948,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>6,48%</t>
+          <t>6,13%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -14003,7 +14003,7 @@
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>5264</t>
+          <t>5343</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -14018,7 +14018,7 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,57%</t>
         </is>
       </c>
     </row>
@@ -14158,12 +14158,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>8709</t>
+          <t>8964</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>18024</t>
+          <t>17724</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -14173,12 +14173,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>27,05%</t>
+          <t>27,84%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>55,99%</t>
+          <t>55,06%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -14193,12 +14193,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>13631</t>
+          <t>13788</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>24490</t>
+          <t>23640</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -14208,12 +14208,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>35,26%</t>
+          <t>35,67%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>63,35%</t>
+          <t>61,15%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -14228,12 +14228,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>25513</t>
+          <t>25222</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>38951</t>
+          <t>38830</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -14243,12 +14243,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>36,01%</t>
+          <t>35,6%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>54,97%</t>
+          <t>54,8%</t>
         </is>
       </c>
     </row>
@@ -14271,12 +14271,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>6624</t>
+          <t>6987</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>15548</t>
+          <t>15805</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -14286,12 +14286,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>20,58%</t>
+          <t>21,7%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>48,3%</t>
+          <t>49,1%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -14306,12 +14306,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>10127</t>
+          <t>9834</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>19939</t>
+          <t>20021</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -14321,12 +14321,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>26,19%</t>
+          <t>25,44%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>51,57%</t>
+          <t>51,79%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -14341,12 +14341,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>18869</t>
+          <t>18865</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>32562</t>
+          <t>32380</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -14361,7 +14361,7 @@
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>45,96%</t>
+          <t>45,7%</t>
         </is>
       </c>
     </row>
@@ -14384,12 +14384,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>3788</t>
+          <t>3862</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>12067</t>
+          <t>12132</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -14399,12 +14399,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>11,77%</t>
+          <t>12,0%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>37,48%</t>
+          <t>37,69%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -14419,12 +14419,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>739</t>
+          <t>737</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>7352</t>
+          <t>6493</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -14439,7 +14439,7 @@
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>19,02%</t>
+          <t>16,79%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -14454,12 +14454,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>5998</t>
+          <t>5646</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>15538</t>
+          <t>16340</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -14469,12 +14469,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>8,47%</t>
+          <t>7,97%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>21,93%</t>
+          <t>23,06%</t>
         </is>
       </c>
     </row>
@@ -14502,7 +14502,7 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>3943</t>
+          <t>3951</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -14517,7 +14517,7 @@
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>12,25%</t>
+          <t>12,27%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -14532,12 +14532,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>637</t>
+          <t>630</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>6029</t>
+          <t>5365</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -14547,12 +14547,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>15,59%</t>
+          <t>13,88%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -14567,12 +14567,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>687</t>
+          <t>780</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>7048</t>
+          <t>6940</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -14582,12 +14582,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>9,95%</t>
+          <t>9,8%</t>
         </is>
       </c>
     </row>
@@ -14840,12 +14840,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>153210</t>
+          <t>153953</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>183002</t>
+          <t>184043</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -14855,12 +14855,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>45,34%</t>
+          <t>45,56%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>54,15%</t>
+          <t>54,46%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -14875,12 +14875,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>162721</t>
+          <t>162105</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>193139</t>
+          <t>193423</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -14890,12 +14890,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>47,37%</t>
+          <t>47,2%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>56,23%</t>
+          <t>56,31%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -14910,12 +14910,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>323520</t>
+          <t>322179</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>367183</t>
+          <t>366806</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -14925,12 +14925,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>47,48%</t>
+          <t>47,28%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>53,89%</t>
+          <t>53,83%</t>
         </is>
       </c>
     </row>
@@ -14953,12 +14953,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>104584</t>
+          <t>104566</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>132933</t>
+          <t>133219</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -14968,12 +14968,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>30,95%</t>
+          <t>30,94%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>39,34%</t>
+          <t>39,42%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -14988,12 +14988,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>115188</t>
+          <t>115863</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>146023</t>
+          <t>146662</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -15003,12 +15003,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>33,54%</t>
+          <t>33,73%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>42,51%</t>
+          <t>42,7%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -15023,12 +15023,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>228545</t>
+          <t>229603</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>270972</t>
+          <t>272367</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -15038,12 +15038,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>33,54%</t>
+          <t>33,7%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>39,77%</t>
+          <t>39,97%</t>
         </is>
       </c>
     </row>
@@ -15066,12 +15066,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>33233</t>
+          <t>33098</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>54335</t>
+          <t>53877</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -15081,12 +15081,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>9,83%</t>
+          <t>9,79%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>16,08%</t>
+          <t>15,94%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -15101,12 +15101,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>21374</t>
+          <t>21325</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>39137</t>
+          <t>38684</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -15116,12 +15116,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>6,22%</t>
+          <t>6,21%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>11,39%</t>
+          <t>11,26%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -15136,12 +15136,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>58793</t>
+          <t>60167</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>87531</t>
+          <t>85830</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -15151,12 +15151,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>8,63%</t>
+          <t>8,83%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>12,85%</t>
+          <t>12,6%</t>
         </is>
       </c>
     </row>
@@ -15179,12 +15179,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>2969</t>
+          <t>3114</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>11906</t>
+          <t>11841</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -15194,12 +15194,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -15214,12 +15214,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>1396</t>
+          <t>1412</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>8541</t>
+          <t>8417</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -15234,7 +15234,7 @@
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -15249,12 +15249,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>5963</t>
+          <t>5862</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>16925</t>
+          <t>16719</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -15264,12 +15264,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,45%</t>
         </is>
       </c>
     </row>
@@ -15297,7 +15297,7 @@
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>6022</t>
+          <t>5620</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -15312,7 +15312,7 @@
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -15332,7 +15332,7 @@
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>4005</t>
+          <t>3902</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -15347,7 +15347,7 @@
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -15362,12 +15362,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>687</t>
+          <t>1058</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>7312</t>
+          <t>7445</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -15377,12 +15377,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>0,1%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,09%</t>
         </is>
       </c>
     </row>
